--- a/taobao_leather_jackets_with_brands.xlsx
+++ b/taobao_leather_jackets_with_brands.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="123">
   <si>
     <t>순번</t>
   </si>
@@ -91,6 +91,48 @@
     <t>item_1054456462690</t>
   </si>
   <si>
+    <t>item_1082717808296</t>
+  </si>
+  <si>
+    <t>item_963160907330</t>
+  </si>
+  <si>
+    <t>item_1080314843824</t>
+  </si>
+  <si>
+    <t>item_982964565711</t>
+  </si>
+  <si>
+    <t>item_1078044637886</t>
+  </si>
+  <si>
+    <t>item_1079411133222</t>
+  </si>
+  <si>
+    <t>item_967752064868</t>
+  </si>
+  <si>
+    <t>item_1077843058059</t>
+  </si>
+  <si>
+    <t>item_1081834756981</t>
+  </si>
+  <si>
+    <t>item_1076140587381</t>
+  </si>
+  <si>
+    <t>item_1076689119808</t>
+  </si>
+  <si>
+    <t>item_970351720471</t>
+  </si>
+  <si>
+    <t>item_1080314063229</t>
+  </si>
+  <si>
+    <t>item_738083059484</t>
+  </si>
+  <si>
     <t>E1</t>
   </si>
   <si>
@@ -127,6 +169,48 @@
     <t>X31</t>
   </si>
   <si>
+    <t>V154</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>V161</t>
+  </si>
+  <si>
+    <t>V64</t>
+  </si>
+  <si>
+    <t>V82</t>
+  </si>
+  <si>
+    <t>V99</t>
+  </si>
+  <si>
+    <t>W25</t>
+  </si>
+  <si>
+    <t>V93</t>
+  </si>
+  <si>
+    <t>V180</t>
+  </si>
+  <si>
+    <t>V80</t>
+  </si>
+  <si>
+    <t>V87</t>
+  </si>
+  <si>
+    <t>W28</t>
+  </si>
+  <si>
+    <t>V160</t>
+  </si>
+  <si>
+    <t>U22</t>
+  </si>
+  <si>
     <t>Procyon</t>
   </si>
   <si>
@@ -142,6 +226,21 @@
     <t>GRIFFIN</t>
   </si>
   <si>
+    <t>Peter Crouch</t>
+  </si>
+  <si>
+    <t>Vanson</t>
+  </si>
+  <si>
+    <t>Club</t>
+  </si>
+  <si>
+    <t>WESTERN</t>
+  </si>
+  <si>
+    <t>Milano</t>
+  </si>
+  <si>
     <t>양가죽</t>
   </si>
   <si>
@@ -151,6 +250,15 @@
     <t>소가죽</t>
   </si>
   <si>
+    <t>가죽 (수밀크)</t>
+  </si>
+  <si>
+    <t>鹿皮</t>
+  </si>
+  <si>
+    <t>사슴가죽</t>
+  </si>
+  <si>
     <t>불명</t>
   </si>
   <si>
@@ -160,79 +268,37 @@
     <t>한국</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>54</t>
+    <t>47</t>
+  </si>
+  <si>
+    <t>连肩</t>
+  </si>
+  <si>
+    <t>52</t>
   </si>
   <si>
     <t>59</t>
   </si>
   <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
     <t>66</t>
   </si>
   <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>64</t>
+    <t>71</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>63</t>
   </si>
   <si>
     <t>photo_002.jpg</t>
@@ -275,6 +341,48 @@
   </si>
   <si>
     <t>vintage古着皮衣 男士修身机车款头层绵羊皮真皮外套时尚夹克 X31</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 复古机车风美式经典皮夹克头层牛皮外套男士V154</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 复古重工头层牛皮西部印第安流苏夹克外套 V2</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 水貂毛皮草冬季外套整貂大翻领夹克双面可穿V161</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 复古吉普赛长袖流苏摩托车男士皮夹克外套 V64</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 美式A2复古短款宽松飞行员皮夹克外套男女 V82</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 美式复古短款斜拉链机车服皮夹克摩托车外套V99</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 复古磨砂牛皮西部印第安流苏摩托车夹克外套W25</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 美式复古短款斜拉链机车服皮夹克摩托车外套V93</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 复古美式短款拉链款机车服皮夹克摩托车外套V100</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 美式A2复古短款宽松飞行员皮夹克外套男女 V80</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 美式A2复古短款宽松飞行员皮夹克外套男女 V87</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 复古吉普赛长袖流苏摩托车男士皮夹克外套W28</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 水貂毛皮草冬季外套整貂大翻领夹克双面可穿V160</t>
+  </si>
+  <si>
+    <t>vintage古着皮衣 美式复古休闲款夹克外套阿美咔叽男款 鹿皮U22</t>
   </si>
 </sst>
 </file>
@@ -632,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -684,37 +792,37 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2">
         <v>48</v>
       </c>
-      <c r="H2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2">
         <v>60</v>
       </c>
-      <c r="J2" t="s">
-        <v>61</v>
+      <c r="I2">
+        <v>66</v>
+      </c>
+      <c r="J2">
+        <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L2">
         <v>420</v>
       </c>
       <c r="M2" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -725,37 +833,37 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3">
+        <v>41</v>
+      </c>
+      <c r="H3">
         <v>48</v>
       </c>
-      <c r="I3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="I3">
         <v>70</v>
       </c>
+      <c r="J3">
+        <v>61</v>
+      </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="L3">
         <v>150</v>
       </c>
       <c r="M3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -766,37 +874,37 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4">
+        <v>51</v>
+      </c>
+      <c r="H4">
         <v>58</v>
       </c>
+      <c r="I4">
+        <v>74</v>
+      </c>
+      <c r="J4">
+        <v>54</v>
+      </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L4">
         <v>179</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -807,37 +915,37 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5">
         <v>45</v>
       </c>
-      <c r="G5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" t="s">
-        <v>61</v>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="I5">
+        <v>72</v>
+      </c>
+      <c r="J5">
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L5">
         <v>164</v>
       </c>
       <c r="M5" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -848,37 +956,37 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6">
         <v>45</v>
       </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" t="s">
-        <v>55</v>
+      <c r="H6">
+        <v>54</v>
+      </c>
+      <c r="I6">
+        <v>72</v>
+      </c>
+      <c r="J6">
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L6">
         <v>221</v>
       </c>
       <c r="M6" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -889,37 +997,37 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7">
+        <v>56</v>
+      </c>
+      <c r="H7">
         <v>59</v>
       </c>
-      <c r="I7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" t="s">
-        <v>56</v>
+      <c r="I7">
+        <v>79</v>
+      </c>
+      <c r="J7">
+        <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L7">
         <v>212</v>
       </c>
       <c r="M7" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -930,37 +1038,37 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8">
         <v>55</v>
       </c>
-      <c r="I8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
+      <c r="H8">
+        <v>60</v>
+      </c>
+      <c r="I8">
+        <v>82</v>
+      </c>
+      <c r="J8">
+        <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L8">
         <v>213</v>
       </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -971,37 +1079,37 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" t="s">
-        <v>71</v>
+        <v>82</v>
+      </c>
+      <c r="G9">
+        <v>44</v>
+      </c>
+      <c r="H9">
+        <v>66</v>
+      </c>
+      <c r="I9">
+        <v>68</v>
+      </c>
+      <c r="J9">
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L9">
         <v>196</v>
       </c>
       <c r="M9" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1012,37 +1120,37 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" t="s">
-        <v>56</v>
+        <v>81</v>
+      </c>
+      <c r="G10">
+        <v>55</v>
+      </c>
+      <c r="H10">
+        <v>62</v>
+      </c>
+      <c r="I10">
+        <v>65</v>
+      </c>
+      <c r="J10">
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L10">
         <v>203</v>
       </c>
       <c r="M10" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1053,37 +1161,37 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11">
         <v>48</v>
       </c>
-      <c r="H11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" t="s">
-        <v>72</v>
+      <c r="H11">
+        <v>56</v>
+      </c>
+      <c r="I11">
+        <v>66</v>
+      </c>
+      <c r="J11">
+        <v>64</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L11">
         <v>177</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1094,37 +1202,37 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12">
         <v>45</v>
       </c>
-      <c r="G12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" t="s">
-        <v>70</v>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12">
+        <v>72</v>
+      </c>
+      <c r="J12">
+        <v>61</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L12">
         <v>235</v>
       </c>
       <c r="M12" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1135,37 +1243,611 @@
         <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13">
         <v>48</v>
       </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" t="s">
-        <v>69</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="H13">
+        <v>55</v>
+      </c>
+      <c r="I13">
+        <v>67</v>
+      </c>
+      <c r="J13">
         <v>59</v>
       </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L13">
         <v>232</v>
       </c>
       <c r="M13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14">
+        <v>55</v>
+      </c>
+      <c r="H14">
+        <v>61</v>
+      </c>
+      <c r="I14">
+        <v>67</v>
+      </c>
+      <c r="J14">
+        <v>57</v>
+      </c>
+      <c r="K14" t="s">
+        <v>95</v>
+      </c>
+      <c r="L14">
+        <v>13</v>
+      </c>
+      <c r="M14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15">
+        <v>52</v>
+      </c>
+      <c r="H15">
+        <v>67</v>
+      </c>
+      <c r="I15">
+        <v>67</v>
+      </c>
+      <c r="J15">
+        <v>62</v>
+      </c>
+      <c r="K15" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15">
+        <v>15</v>
+      </c>
+      <c r="M15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16">
+        <v>54</v>
+      </c>
+      <c r="H16">
+        <v>57</v>
+      </c>
+      <c r="I16">
+        <v>65</v>
+      </c>
+      <c r="J16">
+        <v>74</v>
+      </c>
+      <c r="K16" t="s">
+        <v>95</v>
+      </c>
+      <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>59</v>
+      </c>
+      <c r="I17">
+        <v>64</v>
+      </c>
+      <c r="J17">
+        <v>62</v>
+      </c>
+      <c r="K17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17">
+        <v>14</v>
+      </c>
+      <c r="M17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18">
+        <v>55</v>
+      </c>
+      <c r="H18">
+        <v>58</v>
+      </c>
+      <c r="I18">
+        <v>58</v>
+      </c>
+      <c r="J18">
+        <v>54</v>
+      </c>
+      <c r="K18" t="s">
+        <v>95</v>
+      </c>
+      <c r="L18">
+        <v>14</v>
+      </c>
+      <c r="M18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19">
+        <v>42</v>
+      </c>
+      <c r="H19">
+        <v>47</v>
+      </c>
+      <c r="I19">
+        <v>52</v>
+      </c>
+      <c r="J19">
+        <v>59</v>
+      </c>
+      <c r="K19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L19">
+        <v>13</v>
+      </c>
+      <c r="M19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20">
+        <v>41</v>
+      </c>
+      <c r="H20">
+        <v>45</v>
+      </c>
+      <c r="I20">
+        <v>71</v>
+      </c>
+      <c r="J20">
+        <v>59</v>
+      </c>
+      <c r="K20" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20">
+        <v>14</v>
+      </c>
+      <c r="M20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21">
+        <v>44</v>
+      </c>
+      <c r="H21">
+        <v>52</v>
+      </c>
+      <c r="I21">
+        <v>55</v>
+      </c>
+      <c r="J21">
+        <v>64</v>
+      </c>
+      <c r="K21" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21">
+        <v>17</v>
+      </c>
+      <c r="M21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22">
+        <v>44</v>
+      </c>
+      <c r="H22">
+        <v>49</v>
+      </c>
+      <c r="I22">
+        <v>57</v>
+      </c>
+      <c r="J22">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
+        <v>95</v>
+      </c>
+      <c r="L22">
+        <v>13</v>
+      </c>
+      <c r="M22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
+      <c r="G23">
+        <v>52</v>
+      </c>
+      <c r="H23">
+        <v>59</v>
+      </c>
+      <c r="I23">
+        <v>65</v>
+      </c>
+      <c r="J23">
+        <v>65</v>
+      </c>
+      <c r="K23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L23">
+        <v>14</v>
+      </c>
+      <c r="M23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24">
+        <v>52</v>
+      </c>
+      <c r="H24">
+        <v>57</v>
+      </c>
+      <c r="I24">
+        <v>62</v>
+      </c>
+      <c r="J24">
+        <v>54</v>
+      </c>
+      <c r="K24" t="s">
+        <v>95</v>
+      </c>
+      <c r="L24">
+        <v>12</v>
+      </c>
+      <c r="M24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" t="s">
+        <v>91</v>
+      </c>
+      <c r="K25" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25">
+        <v>13</v>
+      </c>
+      <c r="M25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J26" t="s">
+        <v>93</v>
+      </c>
+      <c r="K26" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26">
+        <v>17</v>
+      </c>
+      <c r="M26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" t="s">
         <v>86</v>
+      </c>
+      <c r="H27" t="s">
+        <v>89</v>
+      </c>
+      <c r="I27" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27" t="s">
+        <v>94</v>
+      </c>
+      <c r="K27" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27">
+        <v>12</v>
+      </c>
+      <c r="M27" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
